--- a/actionParams/actionParamsList_protocolCore.xlsx
+++ b/actionParams/actionParamsList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\actionParams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820D8D0A-CA49-4117-8110-07348B75C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD20986-3C34-4CC9-ADDA-949D3B72CD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22416" yWindow="1332" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Codice</t>
   </si>
@@ -48,18 +48,12 @@
     <t>Clbfile</t>
   </si>
   <si>
-    <t>Response AX3M (az campo/az bottone di finestra)</t>
-  </si>
-  <si>
     <t>intero</t>
   </si>
   <si>
     <t>Definzione tipologia videata</t>
   </si>
   <si>
-    <t>OBJECT</t>
-  </si>
-  <si>
     <t>Codice oggetto</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>YAX3MRESP</t>
   </si>
   <si>
-    <t>Body per Azione</t>
-  </si>
-  <si>
     <t>per azioni campo/azioni bottone di Finestra</t>
   </si>
   <si>
@@ -105,7 +96,19 @@
     <t>patch</t>
   </si>
   <si>
-    <t>manca</t>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>AAR</t>
+  </si>
+  <si>
+    <t>Response  Azione  AX3M</t>
+  </si>
+  <si>
+    <t>Body della request AX3M</t>
+  </si>
+  <si>
+    <t>OBJET</t>
   </si>
 </sst>
 </file>
@@ -137,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -146,58 +149,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -268,6 +219,47 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -276,44 +268,40 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,160 +583,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="55.85546875" customWidth="1"/>
-    <col min="4" max="4" width="93.7109375" customWidth="1"/>
+    <col min="4" max="4" width="58.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" t="s">
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
